--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q20_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02929263706181764</v>
+        <v>0.01564443656125256</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02929263706181764</v>
+        <v>0.01564443656125256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01559159792152231</v>
+        <v>0.008805995467378916</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02750596128740167</v>
+        <v>0.01453593270451988</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02750596128740167</v>
+        <v>0.01453593270451988</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0137351945959192</v>
+        <v>0.008189275979561098</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0259081017904191</v>
+        <v>0.013574295081276</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0259081017904191</v>
+        <v>0.013574295081276</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01150189752666495</v>
+        <v>0.007369997275508809</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02545551259051857</v>
+        <v>0.01332143269031877</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02545551259051857</v>
+        <v>0.01332143269031877</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008607836529312999</v>
+        <v>0.006309770578449815</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02703273806202666</v>
+        <v>0.01423366387700298</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02703273806202666</v>
+        <v>0.01423366387700298</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006342266863375803</v>
+        <v>0.005688805489587288</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03118480792575975</v>
+        <v>0.01657768252342769</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03118480792575975</v>
+        <v>0.01657768252342769</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006074723399212085</v>
+        <v>0.00593824862144627</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03875874481396444</v>
+        <v>0.02078728707277229</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03875874481396444</v>
+        <v>0.02078728707277229</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006941679815565938</v>
+        <v>0.006757084098323983</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04919941571299859</v>
+        <v>0.02653357605796468</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04919941571299859</v>
+        <v>0.02653357605796468</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008638140199857288</v>
+        <v>0.008222414360583996</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0615199341622789</v>
+        <v>0.03323515470740569</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0615199341622789</v>
+        <v>0.03323515470740569</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01306492133807553</v>
+        <v>0.01113210406844009</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07483960750752838</v>
+        <v>0.0403756969161755</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07483960750752838</v>
+        <v>0.0403756969161755</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01761378035987056</v>
+        <v>0.01447000738750464</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.08769904832155893</v>
+        <v>0.04717647915408591</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08769904832155893</v>
+        <v>0.04717647915408591</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01674768325350445</v>
+        <v>0.0156554336989223</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1016989100195989</v>
+        <v>0.05457917507935205</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1016989100195989</v>
+        <v>0.05457917507935205</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01101839438899509</v>
+        <v>0.01569753467927899</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1187582342677918</v>
+        <v>0.06370663688956513</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1187582342677918</v>
+        <v>0.06370663688956513</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006560701934028864</v>
+        <v>0.01722724684551257</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1380496714154798</v>
+        <v>0.07413492026615431</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1380496714154798</v>
+        <v>0.07413492026615431</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008076843183019385</v>
+        <v>0.02040220634685741</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1569910176419528</v>
+        <v>0.08442863504285231</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1569910176419528</v>
+        <v>0.08442863504285231</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01047857164277438</v>
+        <v>0.02388765034640655</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1725625787814676</v>
+        <v>0.09291666390988529</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1725625787814676</v>
+        <v>0.09291666390988529</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01183083376673036</v>
+        <v>0.02680706740983056</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1864740881465048</v>
+        <v>0.1004752814660824</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1864740881465048</v>
+        <v>0.1004752814660824</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01271174460774899</v>
+        <v>0.02926333256227927</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1963498711058313</v>
+        <v>0.1058202243819582</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1963498711058313</v>
+        <v>0.1058202243819582</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01386087073050366</v>
+        <v>0.03095914131783516</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2033381305660904</v>
+        <v>0.1095514072345997</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2033381305660904</v>
+        <v>0.1095514072345997</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01541377103712527</v>
+        <v>0.03208562996505038</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2064923972879831</v>
+        <v>0.1111744079791871</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2064923972879831</v>
+        <v>0.1111744079791871</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01697972156027191</v>
+        <v>0.0325390727166207</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2085317729137356</v>
+        <v>0.1121768097342069</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2085317729137356</v>
+        <v>0.1121768097342069</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01843947608959477</v>
+        <v>0.03265408782125009</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2061332329932898</v>
+        <v>0.1108059835712306</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2061332329932898</v>
+        <v>0.1108059835712306</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01906190491141824</v>
+        <v>0.03208445504201382</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.2031732436159398</v>
+        <v>0.1091588958021614</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2031732436159398</v>
+        <v>0.1091588958021614</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01933750906052855</v>
+        <v>0.03129088650729545</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1989573099040031</v>
+        <v>0.1068870674375884</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1989573099040031</v>
+        <v>0.1068870674375884</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01907123991292505</v>
+        <v>0.03024069732643467</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1939163431724223</v>
+        <v>0.1042030475670166</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1939163431724223</v>
+        <v>0.1042030475670166</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01847548757920748</v>
+        <v>0.02904863529805608</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1896662777453854</v>
+        <v>0.101919032120516</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1896662777453854</v>
+        <v>0.101919032120516</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01824724853862377</v>
+        <v>0.02818527152886264</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1815960792995887</v>
+        <v>0.09763516635143465</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1815960792995887</v>
+        <v>0.09763516635143465</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01763209088585304</v>
+        <v>0.02666458205712031</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1771343838260299</v>
+        <v>0.09525609494365389</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1771343838260299</v>
+        <v>0.09525609494365389</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01772718141627498</v>
+        <v>0.02566293193825967</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1757597789743011</v>
+        <v>0.09456572403263856</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1757597789743011</v>
+        <v>0.09456572403263856</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01782527568473574</v>
+        <v>0.02496243407516092</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1731866057898327</v>
+        <v>0.09320215320803486</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1731866057898327</v>
+        <v>0.09320215320803486</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01839539584188567</v>
+        <v>0.02489587195130293</v>
       </c>
     </row>
   </sheetData>
